--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:03+00:00</t>
+    <t>2023-03-24T14:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:14+00:00</t>
+    <t>2023-03-24T14:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:14:45+00:00</t>
+    <t>2023-03-24T14:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:11+00:00</t>
+    <t>2023-03-24T14:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:59+00:00</t>
+    <t>2023-03-24T14:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:42:38+00:00</t>
+    <t>2023-03-24T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:20+00:00</t>
+    <t>2023-03-24T15:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:53+00:00</t>
+    <t>2023-03-24T15:38:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:38:14+00:00</t>
+    <t>2023-03-26T08:37:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:37:00+00:00</t>
+    <t>2023-03-26T08:42:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:42:47+00:00</t>
+    <t>2023-03-26T09:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -808,6 +808,9 @@
   </si>
   <si>
     <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>Specimen identifier</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -4826,7 +4829,7 @@
         <v>76</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>76</v>
+        <v>258</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>76</v>
@@ -4865,7 +4868,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4880,21 +4883,21 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4920,29 +4923,29 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>76</v>
@@ -4978,7 +4981,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4993,21 +4996,21 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5033,13 +5036,13 @@
         <v>154</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5053,7 +5056,7 @@
         <v>76</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>76</v>
@@ -5089,7 +5092,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5104,21 +5107,21 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5141,13 +5144,13 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5198,7 +5201,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5213,21 +5216,21 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5250,16 +5253,16 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5309,7 +5312,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5324,21 +5327,21 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5364,10 +5367,10 @@
         <v>142</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5418,7 +5421,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5433,21 +5436,21 @@
         <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>148</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5473,13 +5476,13 @@
         <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5508,10 +5511,10 @@
         <v>172</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5529,7 +5532,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5544,21 +5547,21 @@
         <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5584,13 +5587,13 @@
         <v>179</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5620,7 +5623,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5638,7 +5641,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5653,21 +5656,21 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5773,10 +5776,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5884,10 +5887,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5997,10 +6000,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6045,7 +6048,7 @@
         <v>76</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>76</v>
@@ -6084,7 +6087,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6099,21 +6102,21 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6136,17 +6139,17 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -6195,7 +6198,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6210,10 +6213,10 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -6221,10 +6224,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6247,13 +6250,13 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6304,7 +6307,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6319,21 +6322,21 @@
         <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6356,16 +6359,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6415,7 +6418,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6430,7 +6433,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
@@ -6441,10 +6444,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6467,16 +6470,16 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6526,7 +6529,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6541,21 +6544,21 @@
         <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6578,13 +6581,13 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6635,7 +6638,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6650,21 +6653,21 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6770,10 +6773,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6881,14 +6884,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6910,10 +6913,10 @@
         <v>130</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>133</v>
@@ -6968,7 +6971,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6994,10 +6997,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7020,13 +7023,13 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7077,7 +7080,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7092,21 +7095,21 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7129,13 +7132,13 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7174,17 +7177,17 @@
         <v>76</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7199,24 +7202,24 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>76</v>
@@ -7238,13 +7241,13 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7295,7 +7298,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7310,21 +7313,21 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7347,13 +7350,13 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7404,7 +7407,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7422,7 +7425,7 @@
         <v>76</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>76</v>
@@ -7430,10 +7433,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7456,13 +7459,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7513,7 +7516,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7528,21 +7531,21 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7568,10 +7571,10 @@
         <v>179</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7598,13 +7601,13 @@
         <v>76</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>76</v>
@@ -7622,7 +7625,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7637,21 +7640,21 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7677,13 +7680,13 @@
         <v>179</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7709,13 +7712,13 @@
         <v>76</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>76</v>
@@ -7733,7 +7736,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7748,21 +7751,21 @@
         <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7785,19 +7788,19 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>76</v>
@@ -7825,10 +7828,10 @@
         <v>184</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>76</v>
@@ -7846,7 +7849,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7867,15 +7870,15 @@
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7898,13 +7901,13 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7955,7 +7958,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7970,7 +7973,7 @@
         <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7981,10 +7984,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8090,10 +8093,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8201,14 +8204,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8230,10 +8233,10 @@
         <v>130</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>133</v>
@@ -8288,7 +8291,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8314,10 +8317,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8343,10 +8346,10 @@
         <v>154</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8397,7 +8400,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8412,7 +8415,7 @@
         <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
@@ -8423,10 +8426,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8452,10 +8455,10 @@
         <v>179</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8482,13 +8485,13 @@
         <v>76</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>76</v>
@@ -8506,7 +8509,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8521,7 +8524,7 @@
         <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8532,10 +8535,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8558,13 +8561,13 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8615,7 +8618,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8630,21 +8633,21 @@
         <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8667,13 +8670,13 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8724,7 +8727,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8739,7 +8742,7 @@
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8750,10 +8753,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8776,13 +8779,13 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8833,7 +8836,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8848,7 +8851,7 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>76</v>
@@ -8859,10 +8862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8968,10 +8971,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9079,14 +9082,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9108,10 +9111,10 @@
         <v>130</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>133</v>
@@ -9166,7 +9169,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9192,10 +9195,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9221,10 +9224,10 @@
         <v>142</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9275,7 +9278,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9296,15 +9299,15 @@
         <v>76</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9330,10 +9333,10 @@
         <v>154</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9384,7 +9387,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9399,7 +9402,7 @@
         <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
@@ -9410,10 +9413,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9439,10 +9442,10 @@
         <v>179</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9469,13 +9472,13 @@
         <v>76</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>76</v>
@@ -9493,7 +9496,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9508,21 +9511,21 @@
         <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9545,13 +9548,13 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9602,7 +9605,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9617,21 +9620,21 @@
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9654,13 +9657,13 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9711,7 +9714,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9726,21 +9729,21 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9763,13 +9766,13 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9796,13 +9799,13 @@
         <v>76</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>76</v>
@@ -9820,7 +9823,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9835,21 +9838,21 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9875,16 +9878,16 @@
         <v>179</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>76</v>
@@ -9912,10 +9915,10 @@
         <v>184</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>76</v>
@@ -9933,7 +9936,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9954,15 +9957,15 @@
         <v>76</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9985,13 +9988,13 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10042,7 +10045,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10057,13 +10060,13 @@
         <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:01:05+00:00</t>
+    <t>2023-03-26T09:02:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:02:01+00:00</t>
+    <t>2023-03-26T09:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:07:12+00:00</t>
+    <t>2023-03-26T10:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:39+00:00</t>
+    <t>2023-03-26T10:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:51+00:00</t>
+    <t>2023-03-26T10:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:42:59+00:00</t>
+    <t>2023-03-26T11:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:08:41+00:00</t>
+    <t>2023-03-26T11:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:16:53+00:00</t>
+    <t>2023-03-26T11:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:17:47+00:00</t>
+    <t>2023-03-26T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:23:31+00:00</t>
+    <t>2023-03-27T11:26:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9976,7 +9976,7 @@
         <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:26:57+00:00</t>
+    <t>2023-03-27T11:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:35:12+00:00</t>
+    <t>2023-03-27T12:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:01:10+00:00</t>
+    <t>2023-03-27T12:02:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:02:15+00:00</t>
+    <t>2023-03-27T12:10:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:10:50+00:00</t>
+    <t>2023-03-28T07:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:37:59+00:00</t>
+    <t>2023-03-28T07:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:45:58+00:00</t>
+    <t>2023-03-28T07:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:53:05+00:00</t>
+    <t>2023-03-29T10:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:46:03+00:00</t>
+    <t>2023-03-29T10:52:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:52:43+00:00</t>
+    <t>2023-03-29T11:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T11:10:06+00:00</t>
+    <t>2023-03-31T13:54:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:54:07+00:00</t>
+    <t>2023-03-31T13:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:55:03+00:00</t>
+    <t>2023-04-01T08:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:28:06+00:00</t>
+    <t>2023-04-01T08:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:29:12+00:00</t>
+    <t>2023-04-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:49:37+00:00</t>
+    <t>2023-04-01T08:50:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:50:39+00:00</t>
+    <t>2023-04-03T05:56:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T05:56:04+00:00</t>
+    <t>2023-04-03T09:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:35:38+00:00</t>
+    <t>2023-04-03T09:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:37:11+00:00</t>
+    <t>2023-04-03T09:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$74</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="496">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:57:00+00:00</t>
+    <t>2023-04-03T10:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1171,6 +1174,10 @@
     <t>Specimen.collection.collected[x]</t>
   </si>
   <si>
+    <t>dateTime
+Period</t>
+  </si>
+  <si>
     <t>Collection time</t>
   </si>
   <si>
@@ -1181,9 +1188,6 @@
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>.effectiveTime</t>
   </si>
   <si>
@@ -1375,10 +1379,6 @@
   </si>
   <si>
     <t>Specimen.processing.time[x]</t>
-  </si>
-  <si>
-    <t>dateTime
-Period</t>
   </si>
   <si>
     <t>Date and time of specimen processing</t>
@@ -1671,6 +1671,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2006,7 +2021,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2115,7 +2130,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>83</v>
       </c>
@@ -2226,7 +2241,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>91</v>
       </c>
@@ -2335,7 +2350,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>97</v>
       </c>
@@ -2446,7 +2461,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>103</v>
       </c>
@@ -2557,7 +2572,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>112</v>
       </c>
@@ -2668,7 +2683,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>120</v>
       </c>
@@ -2779,7 +2794,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>128</v>
       </c>
@@ -2890,7 +2905,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>136</v>
       </c>
@@ -3003,7 +3018,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>141</v>
       </c>
@@ -3110,7 +3125,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>150</v>
       </c>
@@ -3221,7 +3236,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>152</v>
       </c>
@@ -3330,7 +3345,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>159</v>
       </c>
@@ -3441,7 +3456,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>166</v>
       </c>
@@ -3554,7 +3569,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>177</v>
       </c>
@@ -3667,7 +3682,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>189</v>
       </c>
@@ -3776,7 +3791,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>191</v>
       </c>
@@ -3887,7 +3902,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>193</v>
       </c>
@@ -4000,7 +4015,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>203</v>
       </c>
@@ -4109,7 +4124,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>205</v>
       </c>
@@ -4220,7 +4235,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>207</v>
       </c>
@@ -4333,7 +4348,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>217</v>
       </c>
@@ -4444,7 +4459,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>225</v>
       </c>
@@ -4555,7 +4570,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>233</v>
       </c>
@@ -4666,7 +4681,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>242</v>
       </c>
@@ -4779,7 +4794,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>252</v>
       </c>
@@ -4892,7 +4907,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>262</v>
       </c>
@@ -5005,7 +5020,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>273</v>
       </c>
@@ -5116,7 +5131,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>282</v>
       </c>
@@ -5225,7 +5240,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>290</v>
       </c>
@@ -5336,7 +5351,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>299</v>
       </c>
@@ -5445,7 +5460,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>304</v>
       </c>
@@ -5556,7 +5571,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>313</v>
       </c>
@@ -5665,7 +5680,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>321</v>
       </c>
@@ -5774,7 +5789,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>322</v>
       </c>
@@ -5885,7 +5900,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>323</v>
       </c>
@@ -5998,7 +6013,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>324</v>
       </c>
@@ -6111,7 +6126,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>326</v>
       </c>
@@ -6222,7 +6237,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>333</v>
       </c>
@@ -6331,7 +6346,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>340</v>
       </c>
@@ -6442,7 +6457,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>346</v>
       </c>
@@ -6553,7 +6568,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>354</v>
       </c>
@@ -6650,7 +6665,7 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>358</v>
@@ -6662,7 +6677,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>360</v>
       </c>
@@ -6771,7 +6786,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>361</v>
       </c>
@@ -6882,7 +6897,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>362</v>
       </c>
@@ -6995,7 +7010,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>367</v>
       </c>
@@ -7104,7 +7119,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>374</v>
       </c>
@@ -7117,7 +7132,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>84</v>
@@ -7132,13 +7147,13 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7177,14 +7192,14 @@
         <v>76</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>378</v>
+        <v>164</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>374</v>
@@ -7211,7 +7226,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>382</v>
       </c>
@@ -7226,13 +7241,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>76</v>
@@ -7244,10 +7259,10 @@
         <v>334</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7322,7 +7337,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>384</v>
       </c>
@@ -7431,7 +7446,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>388</v>
       </c>
@@ -7540,7 +7555,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>394</v>
       </c>
@@ -7649,7 +7664,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>402</v>
       </c>
@@ -7760,7 +7775,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>410</v>
       </c>
@@ -7873,7 +7888,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>419</v>
       </c>
@@ -7982,7 +7997,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>423</v>
       </c>
@@ -8091,7 +8106,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>424</v>
       </c>
@@ -8202,7 +8217,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>425</v>
       </c>
@@ -8315,7 +8330,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>426</v>
       </c>
@@ -8424,7 +8439,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>430</v>
       </c>
@@ -8533,7 +8548,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>435</v>
       </c>
@@ -8642,7 +8657,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>441</v>
       </c>
@@ -8670,13 +8685,13 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8751,12 +8766,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8782,10 +8797,10 @@
         <v>355</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8836,7 +8851,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8851,21 +8866,21 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AL63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="B64" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8969,12 +8984,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9080,12 +9095,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9193,12 +9208,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9224,10 +9239,10 @@
         <v>142</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9278,7 +9293,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9299,15 +9314,15 @@
         <v>76</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
         <v>455</v>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>456</v>
-      </c>
       <c r="B68" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9333,10 +9348,10 @@
         <v>154</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9387,7 +9402,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9402,21 +9417,21 @@
         <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>460</v>
-      </c>
       <c r="B69" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9442,10 +9457,10 @@
         <v>179</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9475,11 +9490,11 @@
         <v>397</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>76</v>
       </c>
@@ -9496,7 +9511,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9517,15 +9532,15 @@
         <v>76</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
         <v>465</v>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>466</v>
-      </c>
       <c r="B70" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9551,10 +9566,10 @@
         <v>389</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9605,7 +9620,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9620,21 +9635,21 @@
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
         <v>470</v>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>471</v>
-      </c>
       <c r="B71" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9660,10 +9675,10 @@
         <v>389</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9714,7 +9729,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9729,21 +9744,21 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AL71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM71" t="s" s="2">
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
         <v>475</v>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="B72" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9766,13 +9781,13 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9802,11 +9817,11 @@
         <v>397</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>481</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>76</v>
       </c>
@@ -9823,7 +9838,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9838,21 +9853,21 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AL72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM72" t="s" s="2">
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
         <v>483</v>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>484</v>
-      </c>
       <c r="B73" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9878,16 +9893,16 @@
         <v>179</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>76</v>
@@ -9915,11 +9930,11 @@
         <v>184</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>76</v>
       </c>
@@ -9936,7 +9951,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9957,15 +9972,15 @@
         <v>76</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
         <v>491</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="B74" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9979,7 +9994,7 @@
         <v>78</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>76</v>
@@ -9988,13 +10003,13 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10045,7 +10060,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10060,16 +10075,34 @@
         <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AM74">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI73">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:19:29+00:00</t>
+    <t>2023-04-03T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:20:09+00:00</t>
+    <t>2023-04-03T10:41:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:41:47+00:00</t>
+    <t>2023-04-04T06:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1174,211 +1174,214 @@
     <t>Specimen.collection.collected[x]</t>
   </si>
   <si>
+    <t>Collection time</t>
+  </si>
+  <si>
+    <t>Time when specimen was collected from subject - the physiologically relevant time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.init</t>
+  </si>
+  <si>
+    <t>SPM-17</t>
+  </si>
+  <si>
+    <t>Specimen.collection.collected[x]:collectedDateTime</t>
+  </si>
+  <si>
+    <t>collectedDateTime</t>
+  </si>
+  <si>
+    <t>Specimen.collection.duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration
+</t>
+  </si>
+  <si>
+    <t>How long it took to collect specimen</t>
+  </si>
+  <si>
+    <t>The span of time over which the collection of a specimen occurred.</t>
+  </si>
+  <si>
+    <t>Specimen.collection.quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {SimpleQuantity}
+</t>
+  </si>
+  <si>
+    <t>The quantity of specimen collected</t>
+  </si>
+  <si>
+    <t>The quantity of specimen collected; for instance the volume of a blood sample, or the physical measurement of an anatomic pathology sample.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].role[classCode=SPEC].player.quantity</t>
+  </si>
+  <si>
+    <t>SPM-12</t>
+  </si>
+  <si>
+    <t>Specimen.collection.method</t>
+  </si>
+  <si>
+    <t>Technique used to perform collection</t>
+  </si>
+  <si>
+    <t>A coded value specifying the technique that is used to perform the procedure.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>The  technique that is used to perform the procedure.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
+  </si>
+  <si>
+    <t>.methodCode</t>
+  </si>
+  <si>
+    <t>SPM-7</t>
+  </si>
+  <si>
+    <t>Specimen.collection.bodySite</t>
+  </si>
+  <si>
+    <t>Anatomical collection site</t>
+  </si>
+  <si>
+    <t>Anatomical location from which the specimen was collected (if subject is a patient). This is the target site.  This element is not used for environmental specimens.</t>
+  </si>
+  <si>
+    <t>If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+  </si>
+  <si>
+    <t>.targetSiteCode</t>
+  </si>
+  <si>
+    <t>SPM-8 and SPM-9</t>
+  </si>
+  <si>
+    <t>Specimen.collection.fastingStatus[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+Duration</t>
+  </si>
+  <si>
+    <t>Whether or how long patient abstained from food and/or drink</t>
+  </si>
+  <si>
+    <t>Abstinence or reduction from some or all food, drink, or both, for a period of time prior to sample collection.</t>
+  </si>
+  <si>
+    <t>Representing fasting status using this element is preferred to representing it with an observation using a 'pre-coordinated code'  such as  LOINC 2005-7 (Calcium [Moles/​time] in 2 hour Urine --12 hours fasting), or  using  a component observation ` such as `Observation.component code`  = LOINC 49541-6 (Fasting status - Reported).</t>
+  </si>
+  <si>
+    <t>Many diagnostic tests require fasting  to facilitate accurate interpretation.</t>
+  </si>
+  <si>
+    <t>Codes describing the fasting status of the patient.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
+  </si>
+  <si>
+    <t>OBR-</t>
+  </si>
+  <si>
+    <t>Specimen.processing</t>
+  </si>
+  <si>
+    <t>Processing and processing step details</t>
+  </si>
+  <si>
+    <t>Details concerning processing and processing steps for the specimen.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].act[code=SPCTRT, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Specimen.processing.id</t>
+  </si>
+  <si>
+    <t>Specimen.processing.extension</t>
+  </si>
+  <si>
+    <t>Specimen.processing.modifierExtension</t>
+  </si>
+  <si>
+    <t>Specimen.processing.description</t>
+  </si>
+  <si>
+    <t>Textual description of procedure</t>
+  </si>
+  <si>
+    <t>Textual description of procedure.</t>
+  </si>
+  <si>
+    <t>.text</t>
+  </si>
+  <si>
+    <t>Specimen.processing.procedure</t>
+  </si>
+  <si>
+    <t>Indicates the treatment step  applied to the specimen</t>
+  </si>
+  <si>
+    <t>A coded value specifying the procedure used to process the specimen.</t>
+  </si>
+  <si>
+    <t>Type indicating the technique used to process the specimen.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
+  </si>
+  <si>
+    <t>Specimen.processing.additive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Substance)
+</t>
+  </si>
+  <si>
+    <t>Material used in the processing step</t>
+  </si>
+  <si>
+    <t>Material used in the processing step.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=CSM].role[classCode=ADTV].code</t>
+  </si>
+  <si>
+    <t>SPM-6</t>
+  </si>
+  <si>
+    <t>Specimen.processing.time[x]</t>
+  </si>
+  <si>
     <t>dateTime
 Period</t>
-  </si>
-  <si>
-    <t>Collection time</t>
-  </si>
-  <si>
-    <t>Time when specimen was collected from subject - the physiologically relevant time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.init</t>
-  </si>
-  <si>
-    <t>SPM-17</t>
-  </si>
-  <si>
-    <t>Specimen.collection.collected[x]:collectedDateTime</t>
-  </si>
-  <si>
-    <t>collectedDateTime</t>
-  </si>
-  <si>
-    <t>Specimen.collection.duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duration
-</t>
-  </si>
-  <si>
-    <t>How long it took to collect specimen</t>
-  </si>
-  <si>
-    <t>The span of time over which the collection of a specimen occurred.</t>
-  </si>
-  <si>
-    <t>Specimen.collection.quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
-</t>
-  </si>
-  <si>
-    <t>The quantity of specimen collected</t>
-  </si>
-  <si>
-    <t>The quantity of specimen collected; for instance the volume of a blood sample, or the physical measurement of an anatomic pathology sample.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].role[classCode=SPEC].player.quantity</t>
-  </si>
-  <si>
-    <t>SPM-12</t>
-  </si>
-  <si>
-    <t>Specimen.collection.method</t>
-  </si>
-  <si>
-    <t>Technique used to perform collection</t>
-  </si>
-  <si>
-    <t>A coded value specifying the technique that is used to perform the procedure.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>The  technique that is used to perform the procedure.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
-  </si>
-  <si>
-    <t>.methodCode</t>
-  </si>
-  <si>
-    <t>SPM-7</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite</t>
-  </si>
-  <si>
-    <t>Anatomical collection site</t>
-  </si>
-  <si>
-    <t>Anatomical location from which the specimen was collected (if subject is a patient). This is the target site.  This element is not used for environmental specimens.</t>
-  </si>
-  <si>
-    <t>If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
-  </si>
-  <si>
-    <t>.targetSiteCode</t>
-  </si>
-  <si>
-    <t>SPM-8 and SPM-9</t>
-  </si>
-  <si>
-    <t>Specimen.collection.fastingStatus[x]</t>
-  </si>
-  <si>
-    <t>CodeableConcept
-Duration</t>
-  </si>
-  <si>
-    <t>Whether or how long patient abstained from food and/or drink</t>
-  </si>
-  <si>
-    <t>Abstinence or reduction from some or all food, drink, or both, for a period of time prior to sample collection.</t>
-  </si>
-  <si>
-    <t>Representing fasting status using this element is preferred to representing it with an observation using a 'pre-coordinated code'  such as  LOINC 2005-7 (Calcium [Moles/​time] in 2 hour Urine --12 hours fasting), or  using  a component observation ` such as `Observation.component code`  = LOINC 49541-6 (Fasting status - Reported).</t>
-  </si>
-  <si>
-    <t>Many diagnostic tests require fasting  to facilitate accurate interpretation.</t>
-  </si>
-  <si>
-    <t>Codes describing the fasting status of the patient.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
-  </si>
-  <si>
-    <t>OBR-</t>
-  </si>
-  <si>
-    <t>Specimen.processing</t>
-  </si>
-  <si>
-    <t>Processing and processing step details</t>
-  </si>
-  <si>
-    <t>Details concerning processing and processing steps for the specimen.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].act[code=SPCTRT, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Specimen.processing.id</t>
-  </si>
-  <si>
-    <t>Specimen.processing.extension</t>
-  </si>
-  <si>
-    <t>Specimen.processing.modifierExtension</t>
-  </si>
-  <si>
-    <t>Specimen.processing.description</t>
-  </si>
-  <si>
-    <t>Textual description of procedure</t>
-  </si>
-  <si>
-    <t>Textual description of procedure.</t>
-  </si>
-  <si>
-    <t>.text</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure</t>
-  </si>
-  <si>
-    <t>Indicates the treatment step  applied to the specimen</t>
-  </si>
-  <si>
-    <t>A coded value specifying the procedure used to process the specimen.</t>
-  </si>
-  <si>
-    <t>Type indicating the technique used to process the specimen.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
-  </si>
-  <si>
-    <t>Specimen.processing.additive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Substance)
-</t>
-  </si>
-  <si>
-    <t>Material used in the processing step</t>
-  </si>
-  <si>
-    <t>Material used in the processing step.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=CSM].role[classCode=ADTV].code</t>
-  </si>
-  <si>
-    <t>SPM-6</t>
-  </si>
-  <si>
-    <t>Specimen.processing.time[x]</t>
   </si>
   <si>
     <t>Date and time of specimen processing</t>
@@ -6665,7 +6668,7 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>358</v>
@@ -7132,7 +7135,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>84</v>
@@ -7147,13 +7150,13 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7192,14 +7195,14 @@
         <v>76</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>164</v>
+        <v>378</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>374</v>
@@ -7241,13 +7244,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>76</v>
@@ -7259,10 +7262,10 @@
         <v>334</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8685,13 +8688,13 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>375</v>
+        <v>442</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8768,10 +8771,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8797,10 +8800,10 @@
         <v>355</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8851,7 +8854,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8866,7 +8869,7 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>76</v>
@@ -8877,10 +8880,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8986,10 +8989,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9097,10 +9100,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9210,10 +9213,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9239,10 +9242,10 @@
         <v>142</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9293,7 +9296,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9314,15 +9317,15 @@
         <v>76</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9348,10 +9351,10 @@
         <v>154</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9402,7 +9405,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9417,7 +9420,7 @@
         <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
@@ -9428,10 +9431,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9457,10 +9460,10 @@
         <v>179</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9490,10 +9493,10 @@
         <v>397</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>76</v>
@@ -9511,7 +9514,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9532,15 +9535,15 @@
         <v>76</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9566,10 +9569,10 @@
         <v>389</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9620,7 +9623,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9635,21 +9638,21 @@
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9675,10 +9678,10 @@
         <v>389</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9729,7 +9732,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9744,21 +9747,21 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9781,13 +9784,13 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9817,10 +9820,10 @@
         <v>397</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>76</v>
@@ -9838,7 +9841,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9853,21 +9856,21 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9893,16 +9896,16 @@
         <v>179</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>76</v>
@@ -9930,10 +9933,10 @@
         <v>184</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>76</v>
@@ -9951,7 +9954,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9972,15 +9975,15 @@
         <v>76</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10003,13 +10006,13 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10060,7 +10063,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10075,13 +10078,13 @@
         <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:46:45+00:00</t>
+    <t>2023-04-04T06:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:47:21+00:00</t>
+    <t>2023-04-04T07:17:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T07:17:27+00:00</t>
+    <t>2023-04-04T08:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:23:07+00:00</t>
+    <t>2023-04-04T08:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:37:07+00:00</t>
+    <t>2023-04-04T09:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:08:50+00:00</t>
+    <t>2023-04-04T09:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:09:26+00:00</t>
+    <t>2023-04-04T09:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:19:23+00:00</t>
+    <t>2023-04-04T09:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:25:44+00:00</t>
+    <t>2023-04-04T10:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:05:29+00:00</t>
+    <t>2023-04-04T10:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:21:49+00:00</t>
+    <t>2023-04-04T10:30:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:30:43+00:00</t>
+    <t>2023-04-04T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:10+00:00</t>
+    <t>2023-04-04T10:41:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:37+00:00</t>
+    <t>2023-04-04T10:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:49:31+00:00</t>
+    <t>2023-04-04T13:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:12:12+00:00</t>
+    <t>2023-04-04T13:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:39:29+00:00</t>
+    <t>2023-04-17T11:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:49:04+00:00</t>
+    <t>2023-04-17T12:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:05:39+00:00</t>
+    <t>2023-04-17T12:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:49:16+00:00</t>
+    <t>2023-05-26T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -1694,7 +1694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1781,77 +1781,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:19+00:00</t>
+    <t>2023-05-26T12:35:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:50+00:00</t>
+    <t>2023-05-26T12:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:45:45+00:00</t>
+    <t>2023-05-26T12:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:47:23+00:00</t>
+    <t>2023-05-26T13:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:04:11+00:00</t>
+    <t>2023-05-26T13:05:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:05:32+00:00</t>
+    <t>2023-05-26T13:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:09:55+00:00</t>
+    <t>2023-05-26T14:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:47:38+00:00</t>
+    <t>2023-05-26T14:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:52:17+00:00</t>
+    <t>2023-05-26T14:59:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:59:52+00:00</t>
+    <t>2023-05-26T15:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:03:26+00:00</t>
+    <t>2023-05-26T15:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2614" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:10:57+00:00</t>
+    <t>2023-05-29T05:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -468,11 +468,14 @@
     <t>Id for specimen.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
-    <t>openAtEnd</t>
+    <t>Slice based on the type of identifier.</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>.id</t>
@@ -526,9 +529,6 @@
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -3104,12 +3104,14 @@
       <c r="AB11" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="AC11" s="2"/>
+      <c r="AC11" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>141</v>
@@ -3127,24 +3129,24 @@
         <v>96</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>141</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>76</v>
@@ -3238,21 +3240,21 @@
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3275,13 +3277,13 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3332,7 +3334,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3347,7 +3349,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
@@ -3358,10 +3360,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3390,7 +3392,7 @@
         <v>131</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>133</v>
@@ -3431,16 +3433,16 @@
         <v>76</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>165</v>
@@ -3458,7 +3460,7 @@
         <v>135</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
@@ -3721,13 +3723,13 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3778,7 +3780,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3793,7 +3795,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3836,7 +3838,7 @@
         <v>131</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>133</v>
@@ -3877,16 +3879,16 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>165</v>
@@ -3904,7 +3906,7 @@
         <v>135</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -4054,13 +4056,13 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4111,7 +4113,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4126,7 +4128,7 @@
         <v>76</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
@@ -4169,7 +4171,7 @@
         <v>131</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>133</v>
@@ -4210,16 +4212,16 @@
         <v>76</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>165</v>
@@ -4237,7 +4239,7 @@
         <v>135</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
@@ -4387,7 +4389,7 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>219</v>
@@ -4518,7 +4520,7 @@
         <v>76</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>76</v>
@@ -4609,7 +4611,7 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>235</v>
@@ -4833,7 +4835,7 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>254</v>
@@ -5059,7 +5061,7 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>275</v>
@@ -5465,7 +5467,7 @@
         <v>302</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>303</v>
@@ -5719,13 +5721,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5776,7 +5778,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5791,7 +5793,7 @@
         <v>76</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5834,7 +5836,7 @@
         <v>131</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>133</v>
@@ -5875,16 +5877,16 @@
         <v>76</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>165</v>
@@ -5902,7 +5904,7 @@
         <v>135</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -6052,7 +6054,7 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>254</v>
@@ -6716,13 +6718,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6773,7 +6775,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6788,7 +6790,7 @@
         <v>76</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
@@ -6831,7 +6833,7 @@
         <v>131</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>133</v>
@@ -6899,7 +6901,7 @@
         <v>135</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
@@ -8036,13 +8038,13 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8093,7 +8095,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8108,7 +8110,7 @@
         <v>76</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
@@ -8151,7 +8153,7 @@
         <v>131</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>133</v>
@@ -8219,7 +8221,7 @@
         <v>135</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -8369,7 +8371,7 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>427</v>
@@ -8914,13 +8916,13 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8971,7 +8973,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8986,7 +8988,7 @@
         <v>76</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>76</v>
@@ -9029,7 +9031,7 @@
         <v>131</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>133</v>
@@ -9097,7 +9099,7 @@
         <v>135</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -9319,7 +9321,7 @@
         <v>96</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>76</v>
@@ -9356,7 +9358,7 @@
         <v>76</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>457</v>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-29T05:00:29+00:00</t>
+    <t>2023-05-29T05:09:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-12T13:14:32+00:00</t>
+    <t>2023-06-13T16:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:44:52+00:00</t>
+    <t>2023-06-13T16:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:48:27+00:00</t>
+    <t>2023-06-13T16:56:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:56:41+00:00</t>
+    <t>2023-06-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:39+00:00</t>
+    <t>2023-06-20T13:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-viral-load-specimen.xlsx
+++ b/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:52+00:00</t>
+    <t>2023-06-20T13:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
